--- a/.deploy/菲律宾部署方案-v2.1-修订版.xlsx
+++ b/.deploy/菲律宾部署方案-v2.1-修订版.xlsx
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>g8i.2xlarge（8 vCPU / 32 GiB）；Pod request 2 vCPU / 4 GiB，limit 4 vCPU / 8 GiB</t>
+          <t>g9i.2xlarge（8 vCPU / 32 GiB）；Pod request 2 vCPU / 4 GiB，limit 4 vCPU / 8 GiB</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>g8i.2xlarge（8C32G）</t>
+          <t>g9i.2xlarge（8C32G）</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="D36" s="41" t="inlineStr">
         <is>
-          <t>ACK 命名空间 + 2 × g8i.xlarge（按需）</t>
+          <t>ACK 命名空间 + 2 × g9i.xlarge（按需）</t>
         </is>
       </c>
       <c r="E36" s="51" t="n">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>g8i.2xlarge（8C32G）</t>
+          <t>g9i.2xlarge（8C32G）</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="C14" s="41" t="inlineStr">
         <is>
-          <t>创建 ECS 节点池 4×g8i.2xlarge（跨 2 AZ、ESSD 300G、nofile 调优）</t>
+          <t>创建 ECS 节点池 4×g9i.2xlarge（跨 2 AZ、ESSD 300G、nofile 调优）</t>
         </is>
       </c>
       <c r="D14" s="74" t="inlineStr">
